--- a/tools/importer/reports/import-section-landing.report.xlsx
+++ b/tools/importer/reports/import-section-landing.report.xlsx
@@ -133,7 +133,7 @@
     <t>us/en/magazine</t>
   </si>
   <si>
-    <t>2026-08-05T20:36:01.246Z</t>
+    <t>2026-08-10T10:05:09.459Z</t>
   </si>
   <si>
     <t>Magazine</t>
